--- a/TestData/UploadFiles/Sample_File_Member.xlsx
+++ b/TestData/UploadFiles/Sample_File_Member.xlsx
@@ -334,58 +334,67 @@
     <x:t>3333333333</x:t>
   </x:si>
   <x:si>
+    <x:t>User exists in same organization</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
+    <x:t>2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1111112221</x:t>
+  </x:si>
+  <x:si>
+    <x:t>32323333333</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Email already registered.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The specified role is not valid.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Designation not found</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14</x:t>
+  </x:si>
+  <x:si>
     <x:t>Sorry! You already have maximum numbers of members.</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
-  </x:si>
-  <x:si>
-    <x:t>2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1111112221</x:t>
-  </x:si>
-  <x:si>
-    <x:t>32323333333</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Email already registered.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1710,7 +1719,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="M8" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="N8" s="0" t="s">
         <x:v>104</x:v>
@@ -1718,7 +1727,7 @@
     </x:row>
     <x:row r="9" spans="1:14">
       <x:c r="A9" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>52</x:v>
@@ -1762,7 +1771,7 @@
     </x:row>
     <x:row r="10" spans="1:14">
       <x:c r="A10" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>59</x:v>
@@ -1798,7 +1807,7 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="M10" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="N10" s="0" t="s">
         <x:v>104</x:v>
@@ -1806,7 +1815,7 @@
     </x:row>
     <x:row r="11" spans="1:14">
       <x:c r="A11" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>66</x:v>
@@ -1842,7 +1851,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="M11" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="N11" s="0" t="s">
         <x:v>104</x:v>
@@ -1850,7 +1859,7 @@
     </x:row>
     <x:row r="12" spans="1:14">
       <x:c r="A12" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>72</x:v>
@@ -1894,7 +1903,7 @@
     </x:row>
     <x:row r="13" spans="1:14">
       <x:c r="A13" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>78</x:v>
@@ -1938,7 +1947,7 @@
     </x:row>
     <x:row r="14" spans="1:14">
       <x:c r="A14" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>85</x:v>
@@ -1974,7 +1983,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="M14" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="N14" s="0" t="s">
         <x:v>104</x:v>
@@ -1982,7 +1991,7 @@
     </x:row>
     <x:row r="15" spans="1:14">
       <x:c r="A15" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>91</x:v>
@@ -2139,7 +2148,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="N2" s="0" t="s">
         <x:v>104</x:v>
@@ -2183,7 +2192,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="N3" s="0" t="s">
         <x:v>104</x:v>
@@ -2227,7 +2236,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="M4" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="N4" s="0" t="s">
         <x:v>104</x:v>
@@ -2315,7 +2324,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="M6" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="N6" s="0" t="s">
         <x:v>104</x:v>
@@ -2359,7 +2368,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="M7" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="N7" s="0" t="s">
         <x:v>104</x:v>
@@ -2403,7 +2412,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="M8" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="N8" s="0" t="s">
         <x:v>104</x:v>
@@ -2411,7 +2420,7 @@
     </x:row>
     <x:row r="9" spans="1:14">
       <x:c r="A9" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
         <x:v>52</x:v>
@@ -2447,7 +2456,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="M9" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="N9" s="0" t="s">
         <x:v>104</x:v>
@@ -2455,7 +2464,7 @@
     </x:row>
     <x:row r="10" spans="1:14">
       <x:c r="A10" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
         <x:v>59</x:v>
@@ -2491,7 +2500,7 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="M10" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="N10" s="0" t="s">
         <x:v>104</x:v>
@@ -2499,7 +2508,7 @@
     </x:row>
     <x:row r="11" spans="1:14">
       <x:c r="A11" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
         <x:v>66</x:v>
@@ -2535,7 +2544,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="M11" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="N11" s="0" t="s">
         <x:v>104</x:v>
@@ -2543,7 +2552,7 @@
     </x:row>
     <x:row r="12" spans="1:14">
       <x:c r="A12" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
         <x:v>72</x:v>
@@ -2579,7 +2588,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="M12" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="N12" s="0" t="s">
         <x:v>104</x:v>
@@ -2587,7 +2596,7 @@
     </x:row>
     <x:row r="13" spans="1:14">
       <x:c r="A13" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
         <x:v>78</x:v>
@@ -2623,7 +2632,7 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="M13" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="N13" s="0" t="s">
         <x:v>104</x:v>
@@ -2631,7 +2640,7 @@
     </x:row>
     <x:row r="14" spans="1:14">
       <x:c r="A14" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
         <x:v>85</x:v>
@@ -2667,7 +2676,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="M14" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="N14" s="0" t="s">
         <x:v>104</x:v>
@@ -2675,7 +2684,7 @@
     </x:row>
     <x:row r="15" spans="1:14">
       <x:c r="A15" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
         <x:v>91</x:v>
@@ -2711,7 +2720,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="M15" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="N15" s="0" t="s">
         <x:v>104</x:v>

--- a/TestData/UploadFiles/Sample_File_Member.xlsx
+++ b/TestData/UploadFiles/Sample_File_Member.xlsx
@@ -392,9 +392,6 @@
   </x:si>
   <x:si>
     <x:t>14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sorry! You already have maximum numbers of members.</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -2148,7 +2145,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="N2" s="0" t="s">
         <x:v>104</x:v>
@@ -2192,7 +2189,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="N3" s="0" t="s">
         <x:v>104</x:v>
@@ -2236,7 +2233,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="M4" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="N4" s="0" t="s">
         <x:v>104</x:v>
@@ -2324,7 +2321,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="M6" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="N6" s="0" t="s">
         <x:v>104</x:v>
@@ -2368,7 +2365,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="M7" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="N7" s="0" t="s">
         <x:v>104</x:v>
@@ -2412,7 +2409,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="M8" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="N8" s="0" t="s">
         <x:v>104</x:v>
@@ -2456,7 +2453,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="M9" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="N9" s="0" t="s">
         <x:v>104</x:v>
@@ -2500,7 +2497,7 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="M10" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="N10" s="0" t="s">
         <x:v>104</x:v>
@@ -2544,7 +2541,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="M11" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="N11" s="0" t="s">
         <x:v>104</x:v>
@@ -2588,7 +2585,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="M12" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="N12" s="0" t="s">
         <x:v>104</x:v>
@@ -2632,7 +2629,7 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="M13" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="N13" s="0" t="s">
         <x:v>104</x:v>
@@ -2676,7 +2673,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="M14" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="N14" s="0" t="s">
         <x:v>104</x:v>
@@ -2720,7 +2717,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="M15" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="N15" s="0" t="s">
         <x:v>104</x:v>
